--- a/PERSONEL.xlsx
+++ b/PERSONEL.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F542C1A1-6B9B-4950-B2E1-916CEAE77FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA304EFF-4D5C-4A38-BF7E-3447DDCE2155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MERSİN" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MERSİN!$E$1:$E$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MERSİN!$E$1:$E$95</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="125">
   <si>
     <t>AHMET ÇELİK</t>
   </si>
@@ -175,12 +175,6 @@
   </si>
   <si>
     <t>MEHMET SARI</t>
-  </si>
-  <si>
-    <t>MEHMET AKGÜN KOLUKIRIK</t>
-  </si>
-  <si>
-    <t>MEHMET NEJAT AY</t>
   </si>
   <si>
     <t>MEHMET ZÜLFÜ DEMİRAĞ</t>
@@ -880,2151 +874,2109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G95"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="9"/>
+    <col min="7" max="7" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" s="3">
         <v>44142</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1">
         <v>3242801113</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3" s="3">
         <v>41452</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1">
         <v>3242802020</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4" s="3">
         <v>30627</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1">
         <v>3242801121</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C5" s="3">
         <v>41146</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F5" s="1">
         <v>3242801082</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C6" s="3">
         <v>32659</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F6" s="1">
         <v>3242801200</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="3">
         <v>35027</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
         <v>3242801115</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" s="3">
         <v>42642</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F8" s="1">
         <v>3242801360</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C9" s="3">
         <v>38638</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F9" s="1">
         <v>3242801362</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C10" s="7">
         <v>44582</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3">
         <v>37472</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1">
         <v>3242801114</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3">
         <v>29517</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C13" s="3">
-        <v>46005</v>
+        <v>31404</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="1">
+        <v>3242801532</v>
+      </c>
       <c r="G13" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C14" s="3">
-        <v>31404</v>
+        <v>45713</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F14" s="1">
-        <v>3242801532</v>
+        <v>3242802024</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C15" s="3">
-        <v>45713</v>
+        <v>30948</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="3">
+        <v>45725</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="1">
-        <v>3242802024</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="3">
-        <v>30948</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="F16" s="1">
+        <v>3242801193</v>
+      </c>
       <c r="G16" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C17" s="3">
-        <v>45725</v>
+        <v>39307</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E17" s="1"/>
       <c r="F17" s="1">
-        <v>3242801193</v>
+        <v>3242802018</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C18" s="3">
-        <v>39307</v>
+        <v>44383</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F18" s="1">
-        <v>3242802018</v>
+        <v>3242801071</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="C19" s="3">
-        <v>33925</v>
+        <v>41006</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F19" s="1">
-        <v>3242801185</v>
+        <v>3242801201</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C20" s="3">
-        <v>44383</v>
+        <v>41007</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="1">
-        <v>3242801071</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="C21" s="3">
-        <v>41006</v>
+        <v>43446</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F21" s="1">
-        <v>3242801201</v>
-      </c>
+      <c r="F21" s="1"/>
       <c r="G21" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C22" s="3">
-        <v>41007</v>
+        <v>454746</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3242801163</v>
+      </c>
       <c r="G22" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C23" s="3">
-        <v>43446</v>
+        <v>454516</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F23" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1">
+        <v>3242801125</v>
+      </c>
       <c r="G23" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3">
-        <v>454746</v>
+        <v>454709</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F24" s="1">
-        <v>3242801163</v>
+        <v>3242801195</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C25" s="3">
-        <v>454516</v>
+        <v>454710</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1">
-        <v>3242801125</v>
+        <v>3242802018</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>98</v>
+        <v>3</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C26" s="3">
-        <v>454709</v>
+        <v>31039</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F26" s="1">
-        <v>3242801195</v>
+        <v>3242801084</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C27" s="3">
-        <v>454710</v>
+        <v>31164</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F27" s="1">
-        <v>3242802018</v>
+        <v>3242801073</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C28" s="3">
-        <v>31039</v>
+        <v>27048</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E28" s="1"/>
       <c r="F28" s="1">
-        <v>3242801084</v>
+        <v>3242801120</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C29" s="3">
-        <v>31164</v>
+        <v>23502</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>116</v>
       </c>
       <c r="F29" s="1">
-        <v>3242801073</v>
+        <v>3242801365</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C30" s="3">
-        <v>27048</v>
+        <v>32414</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="F30" s="1">
-        <v>3242801120</v>
+        <v>3242801538</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>111</v>
+        <v>54</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="C31" s="3">
-        <v>23502</v>
+        <v>31048</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3242801537</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="3">
+        <v>29172</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="1">
+        <v>3242801535</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="3">
+        <v>26807</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33" s="1">
+        <v>3242801197</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="3">
+        <v>32400</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" s="1">
+        <v>3242801546</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="3">
+        <v>28763</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F31" s="1">
-        <v>3242801365</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="3">
-        <v>32414</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" s="1">
-        <v>3242801538</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="3">
-        <v>31048</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F33" s="1">
-        <v>3242801537</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" s="3">
-        <v>29172</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" s="1">
-        <v>3242801535</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C35" s="3">
-        <v>26807</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1">
+        <v>3242801167</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="3">
+        <v>41762</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F35" s="1">
-        <v>3242801197</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" s="3">
-        <v>32400</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="F36" s="1">
-        <v>3242801546</v>
+        <v>3242801543</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C37" s="3">
-        <v>28763</v>
+        <v>28287</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F37" s="1">
-        <v>3242801167</v>
+        <v>3242801086</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C38" s="3">
-        <v>41762</v>
+        <v>25436</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F38" s="1">
-        <v>3242801543</v>
+        <v>3242801369</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C39" s="3">
-        <v>28287</v>
+        <v>41033</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E39" s="1"/>
       <c r="F39" s="1">
-        <v>3242801086</v>
+        <v>3242801131</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C40" s="3">
-        <v>25436</v>
+        <v>29481</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F40" s="1">
-        <v>3242801369</v>
+        <v>3242801541</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C41" s="3">
-        <v>41033</v>
+        <v>28330</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1">
-        <v>3242801131</v>
+        <v>3242802026</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C42" s="3">
-        <v>29481</v>
+        <v>27625</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F42" s="1">
-        <v>3242801541</v>
+        <v>3242801373</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C43" s="3">
-        <v>28330</v>
+        <v>41717</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1">
-        <v>3242802026</v>
+        <v>3242802027</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C44" s="3">
-        <v>27625</v>
+        <v>26939</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F44" s="1">
-        <v>3242801373</v>
+        <v>3242801192</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C45" s="3">
-        <v>41717</v>
+        <v>41520</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1">
-        <v>3242802027</v>
+        <v>3242801134</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C46" s="3">
-        <v>26939</v>
+        <v>26938</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F46" s="1">
-        <v>3242801192</v>
+        <v>3242801168</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>100</v>
+        <v>19</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="C47" s="3">
-        <v>41520</v>
+        <v>31344</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1">
-        <v>3242801134</v>
+        <v>3242802023</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" s="3">
-        <v>26938</v>
+        <v>41755</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E48" s="1"/>
       <c r="F48" s="1">
-        <v>3242801168</v>
+        <v>3242801135</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>101</v>
+        <v>8</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C49" s="3">
-        <v>31344</v>
+        <v>46300</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E49" s="1"/>
-      <c r="F49" s="1">
-        <v>3242802023</v>
-      </c>
+      <c r="F49" s="1"/>
       <c r="G49" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C50" s="3">
-        <v>41755</v>
+        <v>46390</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E50" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="F50" s="1">
-        <v>3242801135</v>
+        <v>3242801190</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C51" s="3">
-        <v>46300</v>
+        <v>35445</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
+      <c r="F51" s="1">
+        <v>3242801129</v>
+      </c>
       <c r="G51" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C52" s="3">
-        <v>46390</v>
+        <v>46220</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F52" s="1">
-        <v>3242801190</v>
+        <v>3242801087</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C53" s="3">
-        <v>35445</v>
+        <v>44950</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1">
-        <v>3242801129</v>
+        <v>3242801133</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C54" s="3">
-        <v>46220</v>
+        <v>40368</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>116</v>
       </c>
       <c r="F54" s="1">
-        <v>3242801087</v>
+        <v>3242801371</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C55" s="3">
-        <v>44950</v>
+        <v>32444</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E55" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="F55" s="1">
-        <v>3242801133</v>
+        <v>3242801189</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C56" s="3">
-        <v>40368</v>
+        <v>41037</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E56" s="1"/>
       <c r="F56" s="1">
-        <v>3242801371</v>
+        <v>3242801187</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C57" s="3">
-        <v>32444</v>
+        <v>41339</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>117</v>
       </c>
       <c r="F57" s="1">
-        <v>3242801189</v>
+        <v>3242801549</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C58" s="3">
-        <v>41037</v>
+        <v>31043</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1">
-        <v>3242801187</v>
+        <v>3242801123</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C59" s="3">
-        <v>41339</v>
+        <v>42777</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E59" s="1"/>
       <c r="F59" s="1">
-        <v>3242801549</v>
+        <v>3242801136</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C60" s="3">
-        <v>31043</v>
+        <v>45449</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E60" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="F60" s="1">
-        <v>3242801123</v>
+        <v>3242801191</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C61" s="3">
-        <v>42777</v>
+        <v>33999</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E61" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="F61" s="1">
-        <v>3242801136</v>
+        <v>3242801540</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C62" s="3">
-        <v>45449</v>
+        <v>41090</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E62" s="1"/>
       <c r="F62" s="1">
-        <v>3242801191</v>
+        <v>3242802022</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C63" s="3">
-        <v>33999</v>
+        <v>31085</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F63" s="1">
-        <v>3242801540</v>
+        <v>3242801169</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C64" s="3">
-        <v>41090</v>
+        <v>32281</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1">
-        <v>3242802022</v>
+        <v>3242801132</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C65" s="3">
-        <v>31085</v>
+        <v>39331</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F65" s="1">
-        <v>3242801169</v>
+        <v>3242801188</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C66" s="3">
-        <v>32281</v>
+        <v>27723</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E66" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="F66" s="1">
-        <v>3242801132</v>
+        <v>3242801375</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C67" s="3">
-        <v>39331</v>
+        <v>32337</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" s="1">
+        <v>3242801077</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C68" s="3">
+        <v>31312</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F67" s="1">
-        <v>3242801188</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C68" s="3">
-        <v>27723</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="F68" s="1">
-        <v>3242801375</v>
+        <v>3242801544</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C69" s="3">
-        <v>32337</v>
+        <v>35434</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F69" s="1">
-        <v>3242801077</v>
+        <v>3242801186</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C70" s="3">
-        <v>31312</v>
+        <v>41821</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E70" s="1"/>
       <c r="F70" s="1">
-        <v>3242801544</v>
+        <v>3242801126</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C71" s="3">
-        <v>35434</v>
+        <v>41348</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F71" s="1">
-        <v>3242801186</v>
+        <v>3242801074</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C72" s="3">
-        <v>41821</v>
+        <v>31223</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E72" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="F72" s="1">
-        <v>3242801126</v>
+        <v>3242801547</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C73" s="3">
-        <v>41348</v>
+        <v>40845</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>116</v>
       </c>
       <c r="F73" s="1">
-        <v>3242801074</v>
+        <v>3242801376</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C74" s="3">
-        <v>31223</v>
+        <v>33457</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E74" s="1"/>
       <c r="F74" s="1">
-        <v>3242801547</v>
+        <v>3242802017</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C75" s="3">
-        <v>40845</v>
+        <v>35780</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F75" s="1">
-        <v>3242801376</v>
+        <v>3242801200</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>101</v>
+        <v>64</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="C76" s="3">
-        <v>33457</v>
+        <v>48643</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1">
-        <v>3242802017</v>
+        <v>3242802019</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="C77" s="3">
-        <v>35780</v>
+        <v>807767</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>117</v>
       </c>
       <c r="F77" s="1">
-        <v>3242801200</v>
+        <v>3242801548</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>113</v>
+        <v>4</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C78" s="3">
-        <v>48643</v>
+        <v>600872</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E78" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F78" s="1">
-        <v>3242802019</v>
+        <v>3242801076</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C79" s="3">
-        <v>807767</v>
+        <v>807778</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F79" s="1">
+        <v>3242801536</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C80" s="3">
+        <v>601163</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1">
+        <v>3242802026</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C81" s="3">
+        <v>600880</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F81" s="1"/>
+      <c r="G81" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F79" s="1">
-        <v>3242801548</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C80" s="3">
-        <v>600872</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F80" s="1">
-        <v>3242801076</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C81" s="3">
-        <v>807778</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="C82" s="3">
+        <v>807765</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F82" s="1">
+        <v>3242801085</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F81" s="1">
-        <v>3242801536</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C82" s="3">
-        <v>601163</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1">
-        <v>3242802026</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="C83" s="3">
-        <v>600880</v>
+        <v>807780</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F83" s="1">
+        <v>3242801176</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84" s="3">
+        <v>807702</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1">
+        <v>3242802029</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="3">
+        <v>807770</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F83" s="1"/>
-      <c r="G83" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C84" s="3">
-        <v>807765</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F84" s="1">
-        <v>3242801085</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C85" s="3">
-        <v>807780</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="F85" s="1">
-        <v>3242801176</v>
+        <v>3242801539</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C86" s="3">
-        <v>807702</v>
+        <v>600904</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1">
-        <v>3242802029</v>
+        <v>3242801122</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C87" s="3">
-        <v>807770</v>
+        <v>600909</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F87" s="1"/>
+      <c r="G87" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F87" s="1">
-        <v>3242801539</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="C88" s="3">
-        <v>600904</v>
+        <v>905120</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E88" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F88" s="1">
-        <v>3242801122</v>
+        <v>3242801076</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="C89" s="3">
-        <v>600909</v>
+        <v>600840</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F89" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1">
+        <v>3242802028</v>
+      </c>
       <c r="G89" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="C90" s="3">
-        <v>905120</v>
+        <v>600841</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E90" s="1"/>
       <c r="F90" s="1">
-        <v>3242801076</v>
+        <v>3242802028</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="3">
-        <v>600840</v>
+        <v>600850</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1">
         <v>3242802028</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="3">
-        <v>600841</v>
+        <v>600857</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1">
         <v>3242802028</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="3">
-        <v>600850</v>
+        <v>600859</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1">
         <v>3242802028</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="3">
-        <v>600857</v>
+        <v>600862</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1">
         <v>3242802028</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="3">
-        <v>600859</v>
+        <v>600868</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1">
         <v>3242802028</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="3">
-        <v>600862</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1">
-        <v>3242802028</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="3">
-        <v>600868</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1">
-        <v>3242802028</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E97" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E1:E95" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/PERSONEL.xlsx
+++ b/PERSONEL.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA304EFF-4D5C-4A38-BF7E-3447DDCE2155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDCE9A3-5250-4E2F-8545-4C58CBD0BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MERSİN" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MERSİN!$E$1:$E$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MERSİN!$E$1:$E$94</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="124">
   <si>
     <t>AHMET ÇELİK</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>MEHTAP AKDOĞAN</t>
-  </si>
-  <si>
-    <t>MUHAMMED FURKAN KAPLAN</t>
   </si>
   <si>
     <t>MURAT AKAYDIN</t>
@@ -432,14 +429,15 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <charset val="162"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Verdana"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
     <font>
       <b/>
@@ -874,1972 +872,1970 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G95"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G94"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="9"/>
+    <col min="7" max="7" width="8.85546875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="E1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="C2" s="3">
         <v>44142</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1">
         <v>3242801113</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3" s="3">
         <v>41452</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1">
         <v>3242802020</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3">
         <v>30627</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1">
         <v>3242801121</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="3">
         <v>41146</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" s="1">
         <v>3242801082</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="3">
         <v>32659</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F6" s="1">
         <v>3242801200</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="3">
         <v>35027</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
         <v>3242801115</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="3">
         <v>42642</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F8" s="1">
         <v>3242801360</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3">
         <v>38638</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F9" s="1">
         <v>3242801362</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10" s="7">
         <v>44582</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3">
         <v>37472</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1">
         <v>3242801114</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3">
         <v>29517</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="3">
         <v>31404</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F13" s="1">
         <v>3242801532</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="3">
         <v>45713</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F14" s="1">
         <v>3242802024</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="3">
         <v>30948</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3">
         <v>45725</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F16" s="1">
         <v>3242801193</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="3">
         <v>39307</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1">
         <v>3242802018</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="3">
         <v>44383</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F18" s="1">
         <v>3242801071</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C19" s="3">
         <v>41006</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F19" s="1">
         <v>3242801201</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" s="3">
         <v>41007</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="3">
         <v>43446</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" s="3">
         <v>454746</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F22" s="1">
         <v>3242801163</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" s="3">
         <v>454516</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1">
         <v>3242801125</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" s="3">
-        <v>454709</v>
+        <v>454710</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E24" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1">
+        <v>3242802018</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="3">
+        <v>31039</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3242801084</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="3">
+        <v>31164</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3242801073</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="3">
+        <v>27048</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1">
+        <v>3242801120</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="3">
+        <v>23502</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F24" s="1">
-        <v>3242801195</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="3">
-        <v>454710</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1">
-        <v>3242802018</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="3">
-        <v>31039</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" s="1">
-        <v>3242801084</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="3">
-        <v>31164</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F27" s="1">
-        <v>3242801073</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="3">
-        <v>27048</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" s="1"/>
       <c r="F28" s="1">
-        <v>3242801120</v>
+        <v>3242801365</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>109</v>
+        <v>44</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="C29" s="3">
-        <v>23502</v>
+        <v>32414</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>116</v>
       </c>
       <c r="F29" s="1">
-        <v>3242801365</v>
+        <v>3242801538</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C30" s="3">
-        <v>32414</v>
+        <v>31048</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F30" s="1">
-        <v>3242801538</v>
+        <v>3242801537</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C31" s="3">
-        <v>31048</v>
+        <v>29172</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F31" s="1">
-        <v>3242801537</v>
+        <v>3242801535</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C32" s="3">
-        <v>29172</v>
+        <v>26807</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F32" s="1">
-        <v>3242801535</v>
+        <v>3242801197</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>110</v>
+        <v>90</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C33" s="3">
-        <v>26807</v>
+        <v>32400</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F33" s="1">
-        <v>3242801197</v>
+        <v>3242801546</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C34" s="3">
-        <v>32400</v>
+        <v>28763</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>117</v>
       </c>
       <c r="F34" s="1">
-        <v>3242801546</v>
+        <v>3242801167</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="3">
+        <v>41762</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3242801543</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="3">
+        <v>28287</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="1">
+        <v>3242801086</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="3">
+        <v>25436</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="1">
+        <v>3242801369</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="3">
+        <v>41033</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1">
+        <v>3242801131</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="3">
+        <v>29481</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3242801541</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="3">
+        <v>28330</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1">
+        <v>3242802026</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="3">
+        <v>27625</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3242801373</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="3">
+        <v>41717</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1">
+        <v>3242802027</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="3">
+        <v>26939</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F43" s="1">
+        <v>3242801192</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="3">
+        <v>41520</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1">
+        <v>3242801134</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="3">
+        <v>26938</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3242801168</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="3">
-        <v>28763</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F35" s="1">
-        <v>3242801167</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="C46" s="3">
+        <v>31344</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1">
+        <v>3242802023</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="3">
-        <v>41762</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F36" s="1">
-        <v>3242801543</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" s="3">
-        <v>28287</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F37" s="1">
-        <v>3242801086</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" s="3">
-        <v>25436</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F38" s="1">
-        <v>3242801369</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="3">
-        <v>41033</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1">
-        <v>3242801131</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="3">
-        <v>29481</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F40" s="1">
-        <v>3242801541</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C41" s="3">
-        <v>28330</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1">
-        <v>3242802026</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="3">
-        <v>27625</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" s="1">
-        <v>3242801373</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="3">
-        <v>41717</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1">
-        <v>3242802027</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" s="3">
-        <v>26939</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F44" s="1">
-        <v>3242801192</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="3">
-        <v>41520</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1">
-        <v>3242801134</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" s="3">
-        <v>26938</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F46" s="1">
-        <v>3242801168</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="C47" s="3">
-        <v>31344</v>
+        <v>41755</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1">
-        <v>3242802023</v>
+        <v>3242801135</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C48" s="3">
-        <v>41755</v>
+        <v>46300</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E48" s="1"/>
-      <c r="F48" s="1">
-        <v>3242801135</v>
-      </c>
+      <c r="F48" s="1"/>
       <c r="G48" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C49" s="3">
-        <v>46300</v>
+        <v>46390</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" s="1">
+        <v>3242801190</v>
+      </c>
       <c r="G49" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" s="3">
-        <v>46390</v>
+        <v>35445</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E50" s="1"/>
       <c r="F50" s="1">
-        <v>3242801190</v>
+        <v>3242801129</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C51" s="3">
-        <v>35445</v>
+        <v>46220</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E51" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="F51" s="1">
-        <v>3242801129</v>
+        <v>3242801087</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C52" s="3">
-        <v>46220</v>
+        <v>44950</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1">
+        <v>3242801133</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="3">
+        <v>40368</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F53" s="1">
+        <v>3242801371</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" s="3">
+        <v>32444</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F52" s="1">
-        <v>3242801087</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="3">
-        <v>44950</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1">
-        <v>3242801133</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C54" s="3">
-        <v>40368</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1">
+        <v>3242801189</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" s="3">
+        <v>41037</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1">
+        <v>3242801187</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="3">
+        <v>41339</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F54" s="1">
-        <v>3242801371</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" s="3">
-        <v>32444</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F55" s="1">
-        <v>3242801189</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" s="3">
-        <v>41037</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E56" s="1"/>
       <c r="F56" s="1">
-        <v>3242801187</v>
+        <v>3242801549</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C57" s="3">
-        <v>41339</v>
+        <v>31043</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E57" s="1"/>
       <c r="F57" s="1">
-        <v>3242801549</v>
+        <v>3242801123</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C58" s="3">
-        <v>31043</v>
+        <v>42777</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1">
-        <v>3242801123</v>
+        <v>3242801136</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C59" s="3">
-        <v>42777</v>
+        <v>45449</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E59" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F59" s="1">
-        <v>3242801136</v>
+        <v>3242801191</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C60" s="3">
-        <v>45449</v>
+        <v>33999</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F60" s="1">
-        <v>3242801191</v>
+        <v>3242801540</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C61" s="3">
-        <v>33999</v>
+        <v>41090</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E61" s="1"/>
       <c r="F61" s="1">
-        <v>3242801540</v>
+        <v>3242802022</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C62" s="3">
-        <v>41090</v>
+        <v>31085</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E62" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="F62" s="1">
-        <v>3242802022</v>
+        <v>3242801169</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C63" s="3">
-        <v>31085</v>
+        <v>32281</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E63" s="1"/>
       <c r="F63" s="1">
-        <v>3242801169</v>
+        <v>3242801132</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C64" s="3">
-        <v>32281</v>
+        <v>39331</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E64" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F64" s="1">
-        <v>3242801132</v>
+        <v>3242801188</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C65" s="3">
-        <v>39331</v>
+        <v>27723</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>115</v>
       </c>
       <c r="F65" s="1">
-        <v>3242801188</v>
+        <v>3242801375</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C66" s="3">
-        <v>27723</v>
+        <v>32337</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F66" s="1">
-        <v>3242801375</v>
+        <v>3242801077</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C67" s="3">
-        <v>32337</v>
+        <v>31312</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F67" s="1">
-        <v>3242801077</v>
+        <v>3242801544</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C68" s="3">
-        <v>31312</v>
+        <v>35434</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F68" s="1">
-        <v>3242801544</v>
+        <v>3242801186</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C69" s="3">
-        <v>35434</v>
+        <v>41821</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E69" s="1"/>
       <c r="F69" s="1">
-        <v>3242801186</v>
+        <v>3242801126</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C70" s="3">
-        <v>41821</v>
+        <v>41348</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E70" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="F70" s="1">
-        <v>3242801126</v>
+        <v>3242801074</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C71" s="3">
-        <v>41348</v>
+        <v>31223</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E71" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F71" s="1">
+        <v>3242801547</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C72" s="3">
+        <v>40845</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F72" s="1">
+        <v>3242801376</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73" s="3">
+        <v>33457</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1">
+        <v>3242802017</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" s="3">
+        <v>35780</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F71" s="1">
-        <v>3242801074</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C72" s="3">
-        <v>31223</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F72" s="1">
-        <v>3242801547</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C73" s="3">
-        <v>40845</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F73" s="1">
-        <v>3242801376</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C74" s="3">
-        <v>33457</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E74" s="1"/>
       <c r="F74" s="1">
-        <v>3242802017</v>
+        <v>3242801200</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>97</v>
+        <v>63</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C75" s="3">
-        <v>35780</v>
+        <v>48643</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E75" s="1"/>
       <c r="F75" s="1">
-        <v>3242801200</v>
+        <v>3242802019</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>111</v>
+        <v>1</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="C76" s="3">
-        <v>48643</v>
+        <v>807767</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E76" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="F76" s="1">
-        <v>3242802019</v>
+        <v>3242801548</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C77" s="3">
-        <v>807767</v>
+        <v>600872</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F77" s="1">
+        <v>3242801076</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C78" s="3">
+        <v>807778</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F78" s="1">
+        <v>3242801536</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79" s="3">
+        <v>601163</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1">
+        <v>3242802026</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" s="3">
+        <v>600880</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F80" s="1"/>
+      <c r="G80" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C81" s="3">
+        <v>807765</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F81" s="1">
+        <v>3242801085</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" s="3">
+        <v>807780</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F77" s="1">
-        <v>3242801548</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C78" s="3">
-        <v>600872</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F78" s="1">
-        <v>3242801076</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C79" s="3">
-        <v>807778</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F79" s="1">
-        <v>3242801536</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C80" s="3">
-        <v>601163</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1">
-        <v>3242802026</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C81" s="3">
-        <v>600880</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F81" s="1"/>
-      <c r="G81" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C82" s="3">
-        <v>807765</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="F82" s="1">
-        <v>3242801085</v>
+        <v>3242801176</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C83" s="3">
-        <v>807780</v>
+        <v>807702</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E83" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1">
+        <v>3242802029</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F83" s="1">
-        <v>3242801176</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="C84" s="3">
-        <v>807702</v>
+        <v>807770</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E84" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="F84" s="1">
-        <v>3242802029</v>
+        <v>3242801539</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C85" s="3">
-        <v>807770</v>
+        <v>600904</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E85" s="1"/>
       <c r="F85" s="1">
-        <v>3242801539</v>
+        <v>3242801122</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C86" s="3">
-        <v>600904</v>
+        <v>600909</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1">
-        <v>3242801122</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F86" s="1"/>
       <c r="G86" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C87" s="3">
-        <v>600909</v>
+        <v>905120</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F87" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="F87" s="1">
+        <v>3242801076</v>
+      </c>
       <c r="G87" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="C88" s="3">
-        <v>905120</v>
+        <v>600840</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E88" s="1"/>
       <c r="F88" s="1">
-        <v>3242801076</v>
+        <v>3242802028</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="3">
-        <v>600840</v>
+        <v>600841</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1">
@@ -2849,134 +2845,113 @@
         <v>121</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="3">
-        <v>600841</v>
+        <v>600850</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1">
         <v>3242802028</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="3">
-        <v>600850</v>
+        <v>600857</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1">
         <v>3242802028</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="3">
-        <v>600857</v>
+        <v>600859</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1">
         <v>3242802028</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="3">
-        <v>600859</v>
+        <v>600862</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1">
         <v>3242802028</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="3">
-        <v>600862</v>
+        <v>600868</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1">
         <v>3242802028</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="3">
-        <v>600868</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1">
-        <v>3242802028</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E95" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E1:E94" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/PERSONEL.xlsx
+++ b/PERSONEL.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDCE9A3-5250-4E2F-8545-4C58CBD0BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A017F16E-B430-4133-8CE3-00A0CF541749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MERSİN" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MERSİN!$E$1:$E$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MERSİN!#REF!</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="122">
   <si>
     <t>AHMET ÇELİK</t>
   </si>
@@ -345,9 +345,6 @@
     <t>MERSİN KM</t>
   </si>
   <si>
-    <t>Görevli Olduğu Birim</t>
-  </si>
-  <si>
     <t>İp Telefon</t>
   </si>
   <si>
@@ -367,9 +364,6 @@
   </si>
   <si>
     <t>VOLKAN İZCİ</t>
-  </si>
-  <si>
-    <t>Mersin</t>
   </si>
   <si>
     <t>Erdemli</t>
@@ -872,19 +866,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G94"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F94"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="9"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>100</v>
       </c>
@@ -892,7 +885,7 @@
         <v>101</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>102</v>
@@ -901,13 +894,10 @@
         <v>104</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>91</v>
       </c>
@@ -920,20 +910,19 @@
       <c r="D2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1">
+      <c r="E2" s="1">
         <v>3242801113</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="3">
         <v>41452</v>
@@ -941,20 +930,19 @@
       <c r="D3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1">
+      <c r="E3" s="1">
         <v>3242802020</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="3">
         <v>30627</v>
@@ -962,15 +950,14 @@
       <c r="D4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1">
+      <c r="E4" s="1">
         <v>3242801121</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -981,19 +968,16 @@
         <v>41146</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" s="1">
+        <v>111</v>
+      </c>
+      <c r="E5" s="1">
         <v>3242801082</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1004,19 +988,16 @@
         <v>32659</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="1">
+        <v>112</v>
+      </c>
+      <c r="E6" s="1">
         <v>3242801200</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F6" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -1029,15 +1010,14 @@
       <c r="D7" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1">
+      <c r="E7" s="1">
         <v>3242801115</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -1048,19 +1028,16 @@
         <v>42642</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="1">
+        <v>113</v>
+      </c>
+      <c r="E8" s="1">
         <v>3242801360</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1071,19 +1048,16 @@
         <v>38638</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="1">
+        <v>113</v>
+      </c>
+      <c r="E9" s="1">
         <v>3242801362</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
@@ -1097,12 +1071,11 @@
         <v>103</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
@@ -1115,15 +1088,14 @@
       <c r="D11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1">
+      <c r="E11" s="1">
         <v>3242801114</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F11" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
@@ -1137,12 +1109,11 @@
         <v>103</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -1153,19 +1124,16 @@
         <v>31404</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" s="1">
+        <v>114</v>
+      </c>
+      <c r="E13" s="1">
         <v>3242801532</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F13" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>71</v>
       </c>
@@ -1178,17 +1146,14 @@
       <c r="D14" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="E14" s="1">
         <v>3242802024</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>75</v>
       </c>
@@ -1202,12 +1167,11 @@
         <v>103</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>84</v>
       </c>
@@ -1218,19 +1182,16 @@
         <v>45725</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F16" s="1">
+        <v>112</v>
+      </c>
+      <c r="E16" s="1">
         <v>3242801193</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F16" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,15 +1204,14 @@
       <c r="D17" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1">
+      <c r="E17" s="1">
         <v>3242802018</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F17" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>66</v>
       </c>
@@ -1262,42 +1222,36 @@
         <v>44383</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="1">
+        <v>111</v>
+      </c>
+      <c r="E18" s="1">
         <v>3242801071</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F18" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C19" s="3">
         <v>41006</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="1">
+        <v>112</v>
+      </c>
+      <c r="E19" s="1">
         <v>3242801201</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F19" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>87</v>
       </c>
@@ -1311,14 +1265,13 @@
         <v>103</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>93</v>
@@ -1327,17 +1280,14 @@
         <v>43446</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>11</v>
       </c>
@@ -1348,19 +1298,16 @@
         <v>454746</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F22" s="1">
+        <v>114</v>
+      </c>
+      <c r="E22" s="1">
         <v>3242801163</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F22" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -1373,15 +1320,14 @@
       <c r="D23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1">
+      <c r="E23" s="1">
         <v>3242801125</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F23" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>54</v>
       </c>
@@ -1394,66 +1340,59 @@
       <c r="D24" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1">
+      <c r="E24" s="1">
         <v>3242802018</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F24" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" s="3">
         <v>31039</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="1">
+        <v>111</v>
+      </c>
+      <c r="E25" s="1">
         <v>3242801084</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F25" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C26" s="3">
         <v>31164</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="1">
+        <v>111</v>
+      </c>
+      <c r="E26" s="1">
         <v>3242801073</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F26" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C27" s="3">
         <v>27048</v>
@@ -1461,130 +1400,114 @@
       <c r="D27" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1">
+      <c r="E27" s="1">
         <v>3242801120</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F27" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C28" s="3">
         <v>23502</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F28" s="1">
+        <v>113</v>
+      </c>
+      <c r="E28" s="1">
         <v>3242801365</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F28" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" s="3">
         <v>32414</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" s="1">
+        <v>114</v>
+      </c>
+      <c r="E29" s="1">
         <v>3242801538</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F29" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C30" s="3">
         <v>31048</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F30" s="1">
+        <v>114</v>
+      </c>
+      <c r="E30" s="1">
         <v>3242801537</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F30" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C31" s="3">
         <v>29172</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" s="1">
+        <v>114</v>
+      </c>
+      <c r="E31" s="1">
         <v>3242801535</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32" s="3">
         <v>26807</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="1">
+        <v>112</v>
+      </c>
+      <c r="E32" s="1">
         <v>3242801197</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F32" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>90</v>
       </c>
@@ -1595,19 +1518,16 @@
         <v>32400</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="1">
+        <v>114</v>
+      </c>
+      <c r="E33" s="1">
         <v>3242801546</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F33" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>2</v>
       </c>
@@ -1618,19 +1538,16 @@
         <v>28763</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F34" s="1">
+        <v>115</v>
+      </c>
+      <c r="E34" s="1">
         <v>3242801167</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F34" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>12</v>
       </c>
@@ -1641,19 +1558,16 @@
         <v>41762</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F35" s="1">
+        <v>114</v>
+      </c>
+      <c r="E35" s="1">
         <v>3242801543</v>
       </c>
-      <c r="G35" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F35" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>13</v>
       </c>
@@ -1664,19 +1578,16 @@
         <v>28287</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" s="1">
+        <v>111</v>
+      </c>
+      <c r="E36" s="1">
         <v>3242801086</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F36" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>25</v>
       </c>
@@ -1687,19 +1598,16 @@
         <v>25436</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F37" s="1">
+        <v>113</v>
+      </c>
+      <c r="E37" s="1">
         <v>3242801369</v>
       </c>
-      <c r="G37" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F37" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>33</v>
       </c>
@@ -1712,15 +1620,14 @@
       <c r="D38" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1">
+      <c r="E38" s="1">
         <v>3242801131</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F38" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -1731,19 +1638,16 @@
         <v>29481</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="1">
+        <v>114</v>
+      </c>
+      <c r="E39" s="1">
         <v>3242801541</v>
       </c>
-      <c r="G39" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F39" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
@@ -1756,15 +1660,14 @@
       <c r="D40" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1">
+      <c r="E40" s="1">
         <v>3242802026</v>
       </c>
-      <c r="G40" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F40" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>50</v>
       </c>
@@ -1775,19 +1678,16 @@
         <v>27625</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="1">
+        <v>113</v>
+      </c>
+      <c r="E41" s="1">
         <v>3242801373</v>
       </c>
-      <c r="G41" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F41" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>55</v>
       </c>
@@ -1800,15 +1700,14 @@
       <c r="D42" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1">
+      <c r="E42" s="1">
         <v>3242802027</v>
       </c>
-      <c r="G42" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F42" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>60</v>
       </c>
@@ -1819,19 +1718,16 @@
         <v>26939</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F43" s="1">
+        <v>112</v>
+      </c>
+      <c r="E43" s="1">
         <v>3242801192</v>
       </c>
-      <c r="G43" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F43" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>82</v>
       </c>
@@ -1844,15 +1740,14 @@
       <c r="D44" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1">
+      <c r="E44" s="1">
         <v>3242801134</v>
       </c>
-      <c r="G44" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F44" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>88</v>
       </c>
@@ -1863,19 +1758,16 @@
         <v>26938</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F45" s="1">
+        <v>115</v>
+      </c>
+      <c r="E45" s="1">
         <v>3242801168</v>
       </c>
-      <c r="G45" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F45" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -1888,15 +1780,14 @@
       <c r="D46" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1">
+      <c r="E46" s="1">
         <v>3242802023</v>
       </c>
-      <c r="G46" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F46" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>0</v>
       </c>
@@ -1909,15 +1800,14 @@
       <c r="D47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1">
+      <c r="E47" s="1">
         <v>3242801135</v>
       </c>
-      <c r="G47" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F47" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>8</v>
       </c>
@@ -1931,12 +1821,11 @@
         <v>103</v>
       </c>
       <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F48" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>9</v>
       </c>
@@ -1947,19 +1836,16 @@
         <v>46390</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="1">
+        <v>112</v>
+      </c>
+      <c r="E49" s="1">
         <v>3242801190</v>
       </c>
-      <c r="G49" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F49" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
@@ -1972,15 +1858,14 @@
       <c r="D50" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1">
+      <c r="E50" s="1">
         <v>3242801129</v>
       </c>
-      <c r="G50" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F50" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>16</v>
       </c>
@@ -1991,19 +1876,16 @@
         <v>46220</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F51" s="1">
+        <v>111</v>
+      </c>
+      <c r="E51" s="1">
         <v>3242801087</v>
       </c>
-      <c r="G51" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F51" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>27</v>
       </c>
@@ -2016,15 +1898,14 @@
       <c r="D52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1">
+      <c r="E52" s="1">
         <v>3242801133</v>
       </c>
-      <c r="G52" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F52" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>31</v>
       </c>
@@ -2035,19 +1916,16 @@
         <v>40368</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F53" s="1">
+        <v>113</v>
+      </c>
+      <c r="E53" s="1">
         <v>3242801371</v>
       </c>
-      <c r="G53" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F53" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>43</v>
       </c>
@@ -2058,19 +1936,16 @@
         <v>32444</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F54" s="1">
+        <v>112</v>
+      </c>
+      <c r="E54" s="1">
         <v>3242801189</v>
       </c>
-      <c r="G54" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F54" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>45</v>
       </c>
@@ -2083,15 +1958,14 @@
       <c r="D55" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1">
+      <c r="E55" s="1">
         <v>3242801187</v>
       </c>
-      <c r="G55" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F55" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>51</v>
       </c>
@@ -2102,19 +1976,16 @@
         <v>41339</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F56" s="1">
+        <v>114</v>
+      </c>
+      <c r="E56" s="1">
         <v>3242801549</v>
       </c>
-      <c r="G56" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F56" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>52</v>
       </c>
@@ -2127,15 +1998,14 @@
       <c r="D57" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1">
+      <c r="E57" s="1">
         <v>3242801123</v>
       </c>
-      <c r="G57" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F57" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
@@ -2148,15 +2018,14 @@
       <c r="D58" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1">
+      <c r="E58" s="1">
         <v>3242801136</v>
       </c>
-      <c r="G58" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F58" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
@@ -2167,19 +2036,16 @@
         <v>45449</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F59" s="1">
+        <v>112</v>
+      </c>
+      <c r="E59" s="1">
         <v>3242801191</v>
       </c>
-      <c r="G59" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F59" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>61</v>
       </c>
@@ -2190,19 +2056,16 @@
         <v>33999</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F60" s="1">
+        <v>114</v>
+      </c>
+      <c r="E60" s="1">
         <v>3242801540</v>
       </c>
-      <c r="G60" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F60" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>64</v>
       </c>
@@ -2215,15 +2078,14 @@
       <c r="D61" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1">
+      <c r="E61" s="1">
         <v>3242802022</v>
       </c>
-      <c r="G61" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F61" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>65</v>
       </c>
@@ -2234,19 +2096,16 @@
         <v>31085</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F62" s="1">
+        <v>115</v>
+      </c>
+      <c r="E62" s="1">
         <v>3242801169</v>
       </c>
-      <c r="G62" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F62" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>67</v>
       </c>
@@ -2259,15 +2118,14 @@
       <c r="D63" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1">
+      <c r="E63" s="1">
         <v>3242801132</v>
       </c>
-      <c r="G63" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F63" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>68</v>
       </c>
@@ -2278,19 +2136,16 @@
         <v>39331</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F64" s="1">
+        <v>112</v>
+      </c>
+      <c r="E64" s="1">
         <v>3242801188</v>
       </c>
-      <c r="G64" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F64" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>69</v>
       </c>
@@ -2301,19 +2156,16 @@
         <v>27723</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F65" s="1">
+        <v>113</v>
+      </c>
+      <c r="E65" s="1">
         <v>3242801375</v>
       </c>
-      <c r="G65" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F65" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -2324,19 +2176,16 @@
         <v>32337</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F66" s="1">
+        <v>111</v>
+      </c>
+      <c r="E66" s="1">
         <v>3242801077</v>
       </c>
-      <c r="G66" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F66" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
@@ -2347,19 +2196,16 @@
         <v>31312</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F67" s="1">
+        <v>114</v>
+      </c>
+      <c r="E67" s="1">
         <v>3242801544</v>
       </c>
-      <c r="G67" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F67" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>74</v>
       </c>
@@ -2370,19 +2216,16 @@
         <v>35434</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F68" s="1">
+        <v>112</v>
+      </c>
+      <c r="E68" s="1">
         <v>3242801186</v>
       </c>
-      <c r="G68" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F68" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>77</v>
       </c>
@@ -2395,15 +2238,14 @@
       <c r="D69" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1">
+      <c r="E69" s="1">
         <v>3242801126</v>
       </c>
-      <c r="G69" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F69" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>78</v>
       </c>
@@ -2414,19 +2256,16 @@
         <v>41348</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F70" s="1">
+        <v>111</v>
+      </c>
+      <c r="E70" s="1">
         <v>3242801074</v>
       </c>
-      <c r="G70" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F70" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>79</v>
       </c>
@@ -2437,19 +2276,16 @@
         <v>31223</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F71" s="1">
+        <v>114</v>
+      </c>
+      <c r="E71" s="1">
         <v>3242801547</v>
       </c>
-      <c r="G71" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F71" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>81</v>
       </c>
@@ -2460,19 +2296,16 @@
         <v>40845</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F72" s="1">
+        <v>113</v>
+      </c>
+      <c r="E72" s="1">
         <v>3242801376</v>
       </c>
-      <c r="G72" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F72" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>83</v>
       </c>
@@ -2485,15 +2318,14 @@
       <c r="D73" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1">
+      <c r="E73" s="1">
         <v>3242802017</v>
       </c>
-      <c r="G73" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F73" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>89</v>
       </c>
@@ -2504,24 +2336,21 @@
         <v>35780</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F74" s="1">
+        <v>112</v>
+      </c>
+      <c r="E74" s="1">
         <v>3242801200</v>
       </c>
-      <c r="G74" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F74" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C75" s="3">
         <v>48643</v>
@@ -2529,38 +2358,34 @@
       <c r="D75" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1">
+      <c r="E75" s="1">
         <v>3242802019</v>
       </c>
-      <c r="G75" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F75" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C76" s="3">
         <v>807767</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F76" s="1">
+        <v>114</v>
+      </c>
+      <c r="E76" s="1">
         <v>3242801548</v>
       </c>
-      <c r="G76" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F76" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>4</v>
       </c>
@@ -2571,42 +2396,36 @@
         <v>600872</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F77" s="1">
+        <v>111</v>
+      </c>
+      <c r="E77" s="1">
         <v>3242801076</v>
       </c>
-      <c r="G77" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F77" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C78" s="3">
         <v>807778</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F78" s="1">
+        <v>114</v>
+      </c>
+      <c r="E78" s="1">
         <v>3242801536</v>
       </c>
-      <c r="G78" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F78" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>21</v>
       </c>
@@ -2619,15 +2438,14 @@
       <c r="D79" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1">
+      <c r="E79" s="1">
         <v>3242802026</v>
       </c>
-      <c r="G79" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F79" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>22</v>
       </c>
@@ -2638,68 +2456,59 @@
         <v>600880</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F80" s="1"/>
-      <c r="G80" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C81" s="3">
         <v>807765</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F81" s="1">
+        <v>111</v>
+      </c>
+      <c r="E81" s="1">
         <v>3242801085</v>
       </c>
-      <c r="G81" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F81" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C82" s="3">
         <v>807780</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F82" s="1">
+        <v>115</v>
+      </c>
+      <c r="E82" s="1">
         <v>3242801176</v>
       </c>
-      <c r="G82" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F82" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C83" s="3">
         <v>807702</v>
@@ -2707,38 +2516,34 @@
       <c r="D83" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1">
+      <c r="E83" s="1">
         <v>3242802029</v>
       </c>
-      <c r="G83" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F83" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C84" s="3">
         <v>807770</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F84" s="1">
+        <v>114</v>
+      </c>
+      <c r="E84" s="1">
         <v>3242801539</v>
       </c>
-      <c r="G84" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F84" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>70</v>
       </c>
@@ -2751,15 +2556,14 @@
       <c r="D85" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1">
+      <c r="E85" s="1">
         <v>3242801122</v>
       </c>
-      <c r="G85" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F85" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>85</v>
       </c>
@@ -2770,40 +2574,34 @@
         <v>600909</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F86" s="1"/>
-      <c r="G86" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="E86" s="1"/>
+      <c r="F86" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C87" s="3">
         <v>905120</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F87" s="1">
+        <v>111</v>
+      </c>
+      <c r="E87" s="1">
         <v>3242801076</v>
       </c>
-      <c r="G87" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F87" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>5</v>
       </c>
@@ -2816,15 +2614,14 @@
       <c r="D88" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1">
+      <c r="E88" s="1">
         <v>3242802028</v>
       </c>
-      <c r="G88" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F88" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>7</v>
       </c>
@@ -2837,15 +2634,14 @@
       <c r="D89" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1">
+      <c r="E89" s="1">
         <v>3242802028</v>
       </c>
-      <c r="G89" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F89" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>26</v>
       </c>
@@ -2858,15 +2654,14 @@
       <c r="D90" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1">
+      <c r="E90" s="1">
         <v>3242802028</v>
       </c>
-      <c r="G90" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F90" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>47</v>
       </c>
@@ -2879,15 +2674,14 @@
       <c r="D91" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1">
+      <c r="E91" s="1">
         <v>3242802028</v>
       </c>
-      <c r="G91" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F91" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>48</v>
       </c>
@@ -2900,15 +2694,14 @@
       <c r="D92" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1">
+      <c r="E92" s="1">
         <v>3242802028</v>
       </c>
-      <c r="G92" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F92" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>56</v>
       </c>
@@ -2921,15 +2714,14 @@
       <c r="D93" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1">
+      <c r="E93" s="1">
         <v>3242802028</v>
       </c>
-      <c r="G93" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F93" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>80</v>
       </c>
@@ -2942,16 +2734,14 @@
       <c r="D94" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1">
+      <c r="E94" s="1">
         <v>3242802028</v>
       </c>
-      <c r="G94" s="8" t="s">
-        <v>120</v>
+      <c r="F94" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E94" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/PERSONEL.xlsx
+++ b/PERSONEL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk44142\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A017F16E-B430-4133-8CE3-00A0CF541749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3EF74C-7E92-42FF-8437-6A0976E05195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MERSİN" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="123">
   <si>
     <t>AHMET ÇELİK</t>
   </si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t>ALİ ŞENYURT</t>
+  </si>
+  <si>
+    <t>KENAN ZENGİN</t>
   </si>
 </sst>
 </file>
@@ -866,18 +869,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F94"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F95"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="9"/>
+    <col min="6" max="6" width="8.85546875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>100</v>
       </c>
@@ -897,7 +900,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>91</v>
       </c>
@@ -917,7 +920,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>121</v>
       </c>
@@ -937,7 +940,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -957,7 +960,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -977,7 +980,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -997,7 +1000,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -1017,7 +1020,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
@@ -1075,7 +1078,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>39</v>
       </c>
@@ -1095,7 +1098,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
@@ -1113,7 +1116,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>71</v>
       </c>
@@ -1153,7 +1156,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>75</v>
       </c>
@@ -1171,7 +1174,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>84</v>
       </c>
@@ -1191,7 +1194,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1211,7 +1214,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>66</v>
       </c>
@@ -1231,7 +1234,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>76</v>
       </c>
@@ -1251,7 +1254,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>87</v>
       </c>
@@ -1269,1367 +1272,1363 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C21" s="3">
-        <v>43446</v>
+        <v>43461</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>114</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C22" s="3">
-        <v>454746</v>
+        <v>43446</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="1">
-        <v>3242801163</v>
-      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C23" s="3">
-        <v>454516</v>
+        <v>454746</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E23" s="1">
-        <v>3242801125</v>
+        <v>3242801163</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C24" s="3">
+        <v>454516</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3242801125</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="3">
         <v>454710</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="D25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="1">
         <v>3242802018</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+      <c r="F25" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B26" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C26" s="3">
         <v>31039</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" s="1">
-        <v>3242801084</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" s="3">
-        <v>31164</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>111</v>
       </c>
       <c r="E26" s="1">
+        <v>3242801084</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="3">
+        <v>31164</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="1">
         <v>3242801073</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+      <c r="F27" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B28" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C28" s="3">
         <v>27048</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="D28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="1">
         <v>3242801120</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+      <c r="F28" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C29" s="3">
         <v>23502</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E29" s="1">
         <v>3242801365</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+      <c r="F29" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="3">
-        <v>32414</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" s="1">
-        <v>3242801538</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C30" s="3">
-        <v>31048</v>
+        <v>32414</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>114</v>
       </c>
       <c r="E30" s="1">
-        <v>3242801537</v>
+        <v>3242801538</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31" s="3">
-        <v>29172</v>
+        <v>31048</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>114</v>
       </c>
       <c r="E31" s="1">
-        <v>3242801535</v>
+        <v>3242801537</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>108</v>
       </c>
       <c r="C32" s="3">
+        <v>29172</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3242801535</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="3">
         <v>26807</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E33" s="1">
         <v>3242801197</v>
       </c>
-      <c r="F32" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+      <c r="F33" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="3">
-        <v>32400</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E33" s="1">
-        <v>3242801546</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C34" s="3">
-        <v>28763</v>
+        <v>32400</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E34" s="1">
-        <v>3242801167</v>
+        <v>3242801546</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C35" s="3">
-        <v>41762</v>
+        <v>28763</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E35" s="1">
-        <v>3242801543</v>
+        <v>3242801167</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C36" s="3">
-        <v>28287</v>
+        <v>41762</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E36" s="1">
-        <v>3242801086</v>
+        <v>3242801543</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C37" s="3">
-        <v>25436</v>
+        <v>28287</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E37" s="1">
-        <v>3242801369</v>
+        <v>3242801086</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C38" s="3">
-        <v>41033</v>
+        <v>25436</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E38" s="1">
-        <v>3242801131</v>
+        <v>3242801369</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="3">
-        <v>29481</v>
+        <v>41033</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E39" s="1">
-        <v>3242801541</v>
+        <v>3242801131</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C40" s="3">
-        <v>28330</v>
+        <v>29481</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E40" s="1">
-        <v>3242802026</v>
+        <v>3242801541</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="3">
-        <v>27625</v>
+        <v>28330</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E41" s="1">
-        <v>3242801373</v>
+        <v>3242802026</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="3">
-        <v>41717</v>
+        <v>27625</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E42" s="1">
-        <v>3242802027</v>
+        <v>3242801373</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="3">
-        <v>26939</v>
+        <v>41717</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E43" s="1">
-        <v>3242801192</v>
+        <v>3242802027</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="3">
-        <v>41520</v>
+        <v>26939</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E44" s="1">
-        <v>3242801134</v>
+        <v>3242801192</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="3">
+        <v>41520</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="1">
+        <v>3242801134</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" s="3">
         <v>26938</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E46" s="1">
         <v>3242801168</v>
       </c>
-      <c r="F45" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+      <c r="F46" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B47" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C47" s="3">
         <v>31344</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="D47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="1">
         <v>3242802023</v>
       </c>
-      <c r="F46" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="F47" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" s="3">
-        <v>41755</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="1">
-        <v>3242801135</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C48" s="3">
-        <v>46300</v>
+        <v>41755</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E48" s="1"/>
+      <c r="E48" s="1">
+        <v>3242801135</v>
+      </c>
       <c r="F48" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C49" s="3">
-        <v>46390</v>
+        <v>46300</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E49" s="1">
-        <v>3242801190</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E49" s="1"/>
       <c r="F49" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C50" s="3">
-        <v>35445</v>
+        <v>46390</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E50" s="1">
-        <v>3242801129</v>
+        <v>3242801190</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C51" s="3">
-        <v>46220</v>
+        <v>35445</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E51" s="1">
-        <v>3242801087</v>
+        <v>3242801129</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C52" s="3">
-        <v>44950</v>
+        <v>46220</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E52" s="1">
-        <v>3242801133</v>
+        <v>3242801087</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C53" s="3">
-        <v>40368</v>
+        <v>44950</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E53" s="1">
-        <v>3242801371</v>
+        <v>3242801133</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C54" s="3">
-        <v>32444</v>
+        <v>40368</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E54" s="1">
-        <v>3242801189</v>
+        <v>3242801371</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C55" s="3">
-        <v>41037</v>
+        <v>32444</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E55" s="1">
-        <v>3242801187</v>
+        <v>3242801189</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C56" s="3">
-        <v>41339</v>
+        <v>41037</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E56" s="1">
-        <v>3242801549</v>
+        <v>3242801187</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C57" s="3">
-        <v>31043</v>
+        <v>41339</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E57" s="1">
-        <v>3242801123</v>
+        <v>3242801549</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C58" s="3">
-        <v>42777</v>
+        <v>31043</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>103</v>
       </c>
       <c r="E58" s="1">
-        <v>3242801136</v>
+        <v>3242801123</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C59" s="3">
-        <v>45449</v>
+        <v>42777</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E59" s="1">
-        <v>3242801191</v>
+        <v>3242801136</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C60" s="3">
-        <v>33999</v>
+        <v>45449</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E60" s="1">
-        <v>3242801540</v>
+        <v>3242801191</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C61" s="3">
-        <v>41090</v>
+        <v>33999</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E61" s="1">
-        <v>3242802022</v>
+        <v>3242801540</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C62" s="3">
-        <v>31085</v>
+        <v>41090</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E62" s="1">
-        <v>3242801169</v>
+        <v>3242802022</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C63" s="3">
-        <v>32281</v>
+        <v>31085</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E63" s="1">
-        <v>3242801132</v>
+        <v>3242801169</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C64" s="3">
-        <v>39331</v>
+        <v>32281</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E64" s="1">
-        <v>3242801188</v>
+        <v>3242801132</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C65" s="3">
-        <v>27723</v>
+        <v>39331</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E65" s="1">
-        <v>3242801375</v>
+        <v>3242801188</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C66" s="3">
-        <v>32337</v>
+        <v>27723</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E66" s="1">
-        <v>3242801077</v>
+        <v>3242801375</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C67" s="3">
-        <v>31312</v>
+        <v>32337</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E67" s="1">
-        <v>3242801544</v>
+        <v>3242801077</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C68" s="3">
-        <v>35434</v>
+        <v>31312</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E68" s="1">
-        <v>3242801186</v>
+        <v>3242801544</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C69" s="3">
-        <v>41821</v>
+        <v>35434</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E69" s="1">
-        <v>3242801126</v>
+        <v>3242801186</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C70" s="3">
-        <v>41348</v>
+        <v>41821</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E70" s="1">
-        <v>3242801074</v>
+        <v>3242801126</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C71" s="3">
-        <v>31223</v>
+        <v>41348</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E71" s="1">
-        <v>3242801547</v>
+        <v>3242801074</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C72" s="3">
-        <v>40845</v>
+        <v>31223</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E72" s="1">
-        <v>3242801376</v>
+        <v>3242801547</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C73" s="3">
+        <v>40845</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" s="1">
+        <v>3242801376</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C74" s="3">
         <v>33457</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E73" s="1">
+      <c r="D74" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" s="1">
         <v>3242802017</v>
       </c>
-      <c r="F73" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
+      <c r="F74" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B75" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C75" s="3">
         <v>35780</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E75" s="1">
         <v>3242801200</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F75" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="1" t="s">
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B76" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C76" s="3">
         <v>48643</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E75" s="1">
+      <c r="D76" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E76" s="1">
         <v>3242802019</v>
       </c>
-      <c r="F75" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="1" t="s">
+      <c r="F76" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B77" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C77" s="3">
         <v>807767</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E77" s="1">
         <v>3242801548</v>
       </c>
-      <c r="F76" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="1" t="s">
+      <c r="F77" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B78" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C78" s="3">
         <v>600872</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E78" s="1">
         <v>3242801076</v>
       </c>
-      <c r="F77" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="1" t="s">
+      <c r="F78" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C79" s="3">
         <v>807778</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E79" s="1">
         <v>3242801536</v>
       </c>
-      <c r="F78" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
+      <c r="F79" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C79" s="3">
-        <v>601163</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E79" s="1">
-        <v>3242802026</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C80" s="3">
+        <v>601163</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E80" s="1">
+        <v>3242802026</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="3">
         <v>600880</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E80" s="1"/>
-      <c r="F80" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
+      <c r="E81" s="1"/>
+      <c r="F81" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C81" s="3">
-        <v>807765</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E81" s="1">
-        <v>3242801085</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C82" s="3">
-        <v>807780</v>
+        <v>807765</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E82" s="1">
-        <v>3242801176</v>
+        <v>3242801085</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C83" s="3">
-        <v>807702</v>
+        <v>807780</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E83" s="1">
-        <v>3242802029</v>
+        <v>3242801176</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C84" s="3">
+        <v>807702</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E84" s="1">
+        <v>3242802029</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C85" s="3">
         <v>807770</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E85" s="1">
         <v>3242801539</v>
       </c>
-      <c r="F84" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="1" t="s">
+      <c r="F85" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C85" s="3">
-        <v>600904</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E85" s="1">
-        <v>3242801122</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C86" s="3">
+        <v>600904</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E86" s="1">
+        <v>3242801122</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C87" s="3">
         <v>600909</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E86" s="1"/>
-      <c r="F86" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C87" s="3">
-        <v>905120</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E87" s="1"/>
+      <c r="F87" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C88" s="3">
+        <v>905120</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E88" s="1">
         <v>3242801076</v>
       </c>
-      <c r="F87" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
+      <c r="F88" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="3">
-        <v>600840</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E88" s="1">
-        <v>3242802028</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="3">
-        <v>600841</v>
+        <v>600840</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>103</v>
@@ -2638,18 +2637,18 @@
         <v>3242802028</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="3">
-        <v>600850</v>
+        <v>600841</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>103</v>
@@ -2658,18 +2657,18 @@
         <v>3242802028</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="3">
-        <v>600857</v>
+        <v>600850</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>103</v>
@@ -2681,15 +2680,15 @@
         <v>118</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="3">
-        <v>600859</v>
+        <v>600857</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>103</v>
@@ -2701,15 +2700,15 @@
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="3">
-        <v>600862</v>
+        <v>600859</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>103</v>
@@ -2721,15 +2720,15 @@
         <v>118</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="3">
-        <v>600868</v>
+        <v>600862</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>103</v>
@@ -2738,6 +2737,26 @@
         <v>3242802028</v>
       </c>
       <c r="F94" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="3">
+        <v>600868</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E95" s="1">
+        <v>3242802028</v>
+      </c>
+      <c r="F95" s="8" t="s">
         <v>118</v>
       </c>
     </row>
